--- a/src/nodes/HPC/compressor_stage_1_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_1_blade_stator_coordinates_foil.xlsx
@@ -1023,7 +1023,7 @@
         <v>0.00062619486281547884</v>
       </c>
       <c r="B2">
-        <v>0.00043692109976902258</v>
+        <v>0.00048325951961736795</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0012523897256309577</v>
       </c>
       <c r="B3">
-        <v>0.00071825607010641938</v>
+        <v>0.00078212794611359814</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0018785845884464367</v>
       </c>
       <c r="B4">
-        <v>0.00096816949743390543</v>
+        <v>0.0010455671824778985</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0025047794512619154</v>
       </c>
       <c r="B5">
-        <v>0.0011937137422152219</v>
+        <v>0.0012820072178722044</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0031309743140773942</v>
       </c>
       <c r="B6">
-        <v>0.001397846965270993</v>
+        <v>0.0014949674600224555</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0037571691768928735</v>
       </c>
       <c r="B7">
-        <v>0.0015823065578191196</v>
+        <v>0.001686505382991615</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0043833640397083519</v>
       </c>
       <c r="B8">
-        <v>0.0017481620327253556</v>
+        <v>0.0018578784345972294</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0050095589025238307</v>
       </c>
       <c r="B9">
-        <v>0.0018969992140415316</v>
+        <v>0.0020109666790739489</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.00563575376533931</v>
       </c>
       <c r="B10">
-        <v>0.0020305143961988634</v>
+        <v>0.0021477841677719546</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.0062619486281547884</v>
       </c>
       <c r="B11">
-        <v>0.00215032944396004</v>
+        <v>0.0022702582840864603</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0068881434909702681</v>
       </c>
       <c r="B12">
-        <v>0.0022573466918258413</v>
+        <v>0.0023794542445852822</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.007514338353785747</v>
       </c>
       <c r="B13">
-        <v>0.0023496647829179375</v>
+        <v>0.0024730752664816123</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.0081405332166012249</v>
       </c>
       <c r="B14">
-        <v>0.0024261702050177372</v>
+        <v>0.0025497712003592445</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.0087667280794167038</v>
       </c>
       <c r="B15">
-        <v>0.0024917045159247061</v>
+        <v>0.0026153404296389944</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.0093929229422321826</v>
       </c>
       <c r="B16">
-        <v>0.0025507080234741714</v>
+        <v>0.0026751008581090327</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.010019117805047662</v>
       </c>
       <c r="B17">
-        <v>0.0026000609656268363</v>
+        <v>0.002725299938189932</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.010645312667863142</v>
       </c>
       <c r="B18">
-        <v>0.0026357159625552164</v>
+        <v>0.0027610732546042246</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.011271507530678619</v>
       </c>
       <c r="B19">
-        <v>0.0026574752331536954</v>
+        <v>0.0027821793726498859</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.011897702393494098</v>
       </c>
       <c r="B20">
-        <v>0.0026661033959971235</v>
+        <v>0.0027895326027687511</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.012523897256309577</v>
       </c>
       <c r="B21">
-        <v>0.0026623650696603524</v>
+        <v>0.0027840472554026561</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.013150092119125056</v>
       </c>
       <c r="B22">
-        <v>0.0026468864098264876</v>
+        <v>0.0027664725413408782</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.013776286981940536</v>
       </c>
       <c r="B23">
-        <v>0.002619739720611657</v>
+        <v>0.0027368972727624648</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.014402481844756015</v>
       </c>
       <c r="B24">
-        <v>0.0025808588432402425</v>
+        <v>0.002695245162193903</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.015028676707571494</v>
       </c>
       <c r="B25">
-        <v>0.0025301776189366287</v>
+        <v>0.0026414399221616827</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.015654871570386971</v>
       </c>
       <c r="B26">
-        <v>0.0024676027845723534</v>
+        <v>0.0025753737853019959</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.01628106643320245</v>
       </c>
       <c r="B27">
-        <v>0.0023929326596075738</v>
+        <v>0.002496813064689846</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.016907261296017929</v>
       </c>
       <c r="B28">
-        <v>0.0023059384591496038</v>
+        <v>0.002405492593509943</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.017533456158833408</v>
       </c>
       <c r="B29">
-        <v>0.0022063913983057554</v>
+        <v>0.0023011472049469933</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.01815965102164889</v>
       </c>
       <c r="B30">
-        <v>0.0020941563501125048</v>
+        <v>0.0021836252639745551</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.018785845884464365</v>
       </c>
       <c r="B31">
-        <v>0.0019694728193229809</v>
+        <v>0.0020532292627215816</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.019412040747279844</v>
       </c>
       <c r="B32">
-        <v>0.0018326739686194717</v>
+        <v>0.0019103752251058736</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.020038235610095323</v>
       </c>
       <c r="B33">
-        <v>0.0016840929606842686</v>
+        <v>0.0017554791750452332</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.020664430472910802</v>
       </c>
       <c r="B34">
-        <v>0.0015238957279560936</v>
+        <v>0.0015887578372094206</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.021290625335726284</v>
       </c>
       <c r="B35">
-        <v>0.0013515792818993963</v>
+        <v>0.0014096307392760263</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.021916820198541759</v>
       </c>
       <c r="B36">
-        <v>0.0011664734037350587</v>
+        <v>0.0012173181096746006</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.022543015061357238</v>
       </c>
       <c r="B37">
-        <v>0.0009679078746839603</v>
+        <v>0.0010110401768346905</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.023169209924172717</v>
       </c>
       <c r="B38">
-        <v>0.00075481177481027061</v>
+        <v>0.00078953779447207709</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.023795404786988196</v>
       </c>
       <c r="B39">
-        <v>0.00052451137955130918</v>
+        <v>0.00054963431744746612</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.024421599649803678</v>
       </c>
       <c r="B40">
-        <v>0.00027393226318768292</v>
+        <v>0.00028767372590779439</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.024421599649803678</v>
       </c>
       <c r="B43">
-        <v>0.00013651763598656824</v>
+        <v>0.0001227761732664568</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.023795404786988196</v>
       </c>
       <c r="B44">
-        <v>0.00027328200058973954</v>
+        <v>0.00024815906269358261</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.023169209924172717</v>
       </c>
       <c r="B45">
-        <v>0.00040755157819220557</v>
+        <v>0.00037282555853039904</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.022543015061357238</v>
       </c>
       <c r="B46">
-        <v>0.00053658485317665844</v>
+        <v>0.00049345255102592825</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.021916820198541759</v>
       </c>
       <c r="B47">
-        <v>0.00065802634433964114</v>
+        <v>0.00060718163840009921</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.021290625335726284</v>
       </c>
       <c r="B48">
-        <v>0.00077106470813309829</v>
+        <v>0.0007130132507564684</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.020664430472910802</v>
       </c>
       <c r="B49">
-        <v>0.00087527463542282709</v>
+        <v>0.00081041252616950027</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.020038235610095323</v>
       </c>
       <c r="B50">
-        <v>0.00097023081707462279</v>
+        <v>0.000898844602713658</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.019412040747279844</v>
       </c>
       <c r="B51">
-        <v>0.001055661403755453</v>
+        <v>0.000977960147269051</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.018785845884464365</v>
       </c>
       <c r="B52">
-        <v>0.0011319083853369711</v>
+        <v>0.0010481519419383702</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.01815965102164889</v>
       </c>
       <c r="B53">
-        <v>0.0011994672114920026</v>
+        <v>0.0011099982976299524</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.017533456158833408</v>
       </c>
       <c r="B54">
-        <v>0.001258833331893373</v>
+        <v>0.0011640775252521349</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.016907261296017929</v>
       </c>
       <c r="B55">
-        <v>0.0013103971155462091</v>
+        <v>0.00121084298118587</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.01628106643320245</v>
       </c>
       <c r="B56">
-        <v>0.0013541286087848479</v>
+        <v>0.0012502482037025755</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.015654871570386971</v>
       </c>
       <c r="B57">
-        <v>0.0013898927772759274</v>
+        <v>0.001282121776546285</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.015028676707571494</v>
       </c>
       <c r="B58">
-        <v>0.0014175545866860857</v>
+        <v>0.0013062922834610317</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.014402481844756015</v>
       </c>
       <c r="B59">
-        <v>0.0014369956537036346</v>
+        <v>0.001322609334749974</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.013776286981940536</v>
       </c>
       <c r="B60">
-        <v>0.0014481641991035737</v>
+        <v>0.0013310066469527657</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.013150092119125056</v>
       </c>
       <c r="B61">
-        <v>0.0014510250946825761</v>
+        <v>0.0013314389631681851</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.012523897256309577</v>
       </c>
       <c r="B62">
-        <v>0.001445543212237314</v>
+        <v>0.0013238610264950104</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.011897702393494098</v>
       </c>
       <c r="B63">
-        <v>0.0014318113282808481</v>
+        <v>0.0013083821215092205</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.011271507530678619</v>
       </c>
       <c r="B64">
-        <v>0.0014104338381917883</v>
+        <v>0.0012857296986955977</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.010645312667863142</v>
       </c>
       <c r="B65">
-        <v>0.0013821430420651326</v>
+        <v>0.0012567857500161241</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.010019117805047662</v>
       </c>
       <c r="B66">
-        <v>0.0013476712399958786</v>
+        <v>0.0012224322674327828</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.0093929229422321826</v>
       </c>
       <c r="B67">
-        <v>0.001306779677125556</v>
+        <v>0.0011823868424906947</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.0087667280794167038</v>
       </c>
       <c r="B68">
-        <v>0.0012553453787818246</v>
+        <v>0.0011317094650675366</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.0081405332166012249</v>
       </c>
       <c r="B69">
-        <v>0.0011901602516026612</v>
+        <v>0.0010665592562611539</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.007514338353785747</v>
       </c>
       <c r="B70">
-        <v>0.0011155599472811916</v>
+        <v>0.00099214946371751719</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0068881434909702681</v>
       </c>
       <c r="B71">
-        <v>0.0010362711642314343</v>
+        <v>0.00091416361147199354</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.0062619486281547884</v>
       </c>
       <c r="B72">
-        <v>0.00095104104269583473</v>
+        <v>0.00083111220256941443</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.00563575376533931</v>
       </c>
       <c r="B73">
-        <v>0.000857816680467951</v>
+        <v>0.00074054690889485979</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0050095589025238307</v>
       </c>
       <c r="B74">
-        <v>0.00075732456371735988</v>
+        <v>0.0006433570986849427</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0043833640397083519</v>
       </c>
       <c r="B75">
-        <v>0.00065099801400661593</v>
+        <v>0.000541281612134742</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0037571691768928735</v>
       </c>
       <c r="B76">
-        <v>0.00054031830609416252</v>
+        <v>0.00043611948092166681</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0031309743140773942</v>
       </c>
       <c r="B77">
-        <v>0.00042664201775636596</v>
+        <v>0.00032952152300490327</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0025047794512619154</v>
       </c>
       <c r="B78">
-        <v>0.00031077898564539684</v>
+        <v>0.00022248550998841437</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0018785845884464367</v>
       </c>
       <c r="B79">
-        <v>0.00019419264699397347</v>
+        <v>0.00011679496194998035</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0012523897256309577</v>
       </c>
       <c r="B80">
-        <v>7.9537310034631087E-05</v>
+        <v>1.5665434027452277E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00062619486281547884</v>
       </c>
       <c r="B81">
-        <v>-2.6463098714431795E-05</v>
+        <v>-7.2801518562777215E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.00067715322503109348</v>
       </c>
       <c r="B2">
-        <v>0.00056800259699791</v>
+        <v>0.00066822127430251179</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.001354306450062187</v>
       </c>
       <c r="B3">
-        <v>0.00090576964953195628</v>
+        <v>0.0010439089074382993</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0020314596750932805</v>
       </c>
       <c r="B4">
-        <v>0.001201188028773252</v>
+        <v>0.0013685803060009382</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0027086129001243739</v>
       </c>
       <c r="B5">
-        <v>0.0014648521222092978</v>
+        <v>0.0016558093316680661</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0033857661251554673</v>
       </c>
       <c r="B6">
-        <v>0.00170116429722854</v>
+        <v>0.0019112121917190044</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0040629193501865611</v>
       </c>
       <c r="B7">
-        <v>0.0019126863975592674</v>
+        <v>0.0021380429908496152</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0047400725752176544</v>
       </c>
       <c r="B8">
-        <v>0.0021009727779772338</v>
+        <v>0.0023382625412062216</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0054172258002487478</v>
       </c>
       <c r="B9">
-        <v>0.00226836716937392</v>
+        <v>0.002514850943285238</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0060943790252798412</v>
       </c>
       <c r="B10">
-        <v>0.0024173841425076952</v>
+        <v>0.0026710099984029009</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.0067715322503109346</v>
       </c>
       <c r="B11">
-        <v>0.0025504322514887483</v>
+        <v>0.0028098090228046583</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.0074486854753420288</v>
       </c>
       <c r="B12">
-        <v>0.0026688339201458248</v>
+        <v>0.00293292271442287</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.0081258387003731222</v>
       </c>
       <c r="B13">
-        <v>0.0027696730678300752</v>
+        <v>0.0030365797830083307</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.0088029919254042147</v>
       </c>
       <c r="B14">
-        <v>0.0028512293998739216</v>
+        <v>0.0031185481454677126</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0094801451504353089</v>
       </c>
       <c r="B15">
-        <v>0.002920804270012485</v>
+        <v>0.0031881985355127632</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.010157298375466401</v>
       </c>
       <c r="B16">
-        <v>0.002985094105893924</v>
+        <v>0.0032541254063585432</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.010834451600497496</v>
       </c>
       <c r="B17">
-        <v>0.0030393539824158573</v>
+        <v>0.0033102152724282944</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.01151160482552859</v>
       </c>
       <c r="B18">
-        <v>0.0030774377804568733</v>
+        <v>0.0033485549666007783</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.012188758050559682</v>
       </c>
       <c r="B19">
-        <v>0.0030990359575699834</v>
+        <v>0.0033687405343686464</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.012865911275590777</v>
       </c>
       <c r="B20">
-        <v>0.0031052981154768029</v>
+        <v>0.003372245324378023</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.013543064500621869</v>
       </c>
       <c r="B21">
-        <v>0.003097373855898949</v>
+        <v>0.0033605426852750327</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.014220217725652963</v>
       </c>
       <c r="B22">
-        <v>0.0030762057631418473</v>
+        <v>0.0033348413394858334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.014897370950684058</v>
       </c>
       <c r="B23">
-        <v>0.0030419083518461684</v>
+        <v>0.0032952915045567186</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.015574524175715152</v>
       </c>
       <c r="B24">
-        <v>0.0029943891192363921</v>
+        <v>0.0032417787718140149</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.016251677400746244</v>
       </c>
       <c r="B25">
-        <v>0.0029335555625369988</v>
+        <v>0.0031741887325840482</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.016928830625777335</v>
       </c>
       <c r="B26">
-        <v>0.0028592767306514573</v>
+        <v>0.0030923590666539812</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.017605983850808429</v>
       </c>
       <c r="B27">
-        <v>0.0027712678791991891</v>
+        <v>0.002995935807654314</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.018283137075839524</v>
       </c>
       <c r="B28">
-        <v>0.0026692058154786048</v>
+        <v>0.0028845170776763832</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.018960290300870618</v>
       </c>
       <c r="B29">
-        <v>0.0025527673467881148</v>
+        <v>0.002757700998811524</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.019637443525901712</v>
       </c>
       <c r="B30">
-        <v>0.0024217739158318131</v>
+        <v>0.0026152733108582094</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.020314596750932803</v>
       </c>
       <c r="B31">
-        <v>0.0022766255069365344</v>
+        <v>0.0024577702244434532</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.020991749975963897</v>
       </c>
       <c r="B32">
-        <v>0.0021178667398347971</v>
+        <v>0.0022859155679014033</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.021668903200994991</v>
       </c>
       <c r="B33">
-        <v>0.0019460422342591195</v>
+        <v>0.0021004331695662092</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.022346056426026085</v>
       </c>
       <c r="B34">
-        <v>0.0017614469047266652</v>
+        <v>0.0019017277951374565</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.02302320965105718</v>
       </c>
       <c r="B35">
-        <v>0.0015633768448931721</v>
+        <v>0.0016889279597764745</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.02370036287608827</v>
       </c>
       <c r="B36">
-        <v>0.0013508784431990237</v>
+        <v>0.0014608431160100294</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.024377516101119365</v>
       </c>
       <c r="B37">
-        <v>0.0011229980880846009</v>
+        <v>0.0012162827163648843</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.025054669326150459</v>
       </c>
       <c r="B38">
-        <v>0.0008781792788929146</v>
+        <v>0.00095328317259385834</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.025731822551181553</v>
       </c>
       <c r="B39">
-        <v>0.00061245395857748659</v>
+        <v>0.00066678873335398146</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.026408975776212647</v>
       </c>
       <c r="B40">
-        <v>0.00032125118099446669</v>
+        <v>0.000350970606528336</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.026408975776212647</v>
       </c>
       <c r="B43">
-        <v>0.0001132152022573826</v>
+        <v>8.349577672351336E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.025731822551181553</v>
       </c>
       <c r="B44">
-        <v>0.00023211053514202279</v>
+        <v>0.00017777576036552792</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.025054669326150459</v>
       </c>
       <c r="B45">
-        <v>0.00035245202298630709</v>
+        <v>0.00027734812928536325</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.024377516101119365</v>
       </c>
       <c r="B46">
-        <v>0.00047000569012261672</v>
+        <v>0.00037672106184233339</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.02370036287608827</v>
       </c>
       <c r="B47">
-        <v>0.00058112573352198528</v>
+        <v>0.00047116106071097986</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.02302320965105718</v>
       </c>
       <c r="B48">
-        <v>0.00068451904071005628</v>
+        <v>0.00055896792582675408</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.022346056426026085</v>
       </c>
       <c r="B49">
-        <v>0.0007794806718511274</v>
+        <v>0.00063919978144033628</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.021668903200994991</v>
       </c>
       <c r="B50">
-        <v>0.00086530568710949443</v>
+        <v>0.00071091475180240515</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.020991749975963897</v>
       </c>
       <c r="B51">
-        <v>0.00094152494336855418</v>
+        <v>0.000773476115301948</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.020314596750932803</v>
       </c>
       <c r="B52">
-        <v>0.001008612484388102</v>
+        <v>0.00082746776688118315</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.019637443525901712</v>
       </c>
       <c r="B53">
-        <v>0.0010672781506470333</v>
+        <v>0.00087377875562063623</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.018960290300870618</v>
       </c>
       <c r="B54">
-        <v>0.0011182317826242438</v>
+        <v>0.00091329813060083375</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.018283137075839524</v>
       </c>
       <c r="B55">
-        <v>0.001162026980094158</v>
+        <v>0.00094671571789638</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.017605983850808429</v>
       </c>
       <c r="B56">
-        <v>0.0011985923800133173</v>
+        <v>0.00097392445155819289</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.016928830625777335</v>
       </c>
       <c r="B57">
-        <v>0.0012277003786337925</v>
+        <v>0.00099461804263126881</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.016251677400746244</v>
       </c>
       <c r="B58">
-        <v>0.0012491233722076536</v>
+        <v>0.0010084902021606041</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.015574524175715152</v>
       </c>
       <c r="B59">
-        <v>0.0012626615511930339</v>
+        <v>0.0010152718986154111</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.014897370950684058</v>
       </c>
       <c r="B60">
-        <v>0.0012682262828723151</v>
+        <v>0.0010148431301617647</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.014220217725652963</v>
       </c>
       <c r="B61">
-        <v>0.0012657567287339422</v>
+        <v>0.0010071211523899558</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.013543064500621869</v>
       </c>
       <c r="B62">
-        <v>0.0012551920502663595</v>
+        <v>0.00099202322089027534</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.012865911275590777</v>
       </c>
       <c r="B63">
-        <v>0.0012366676531682609</v>
+        <v>0.000969720444267041</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.012188758050559682</v>
       </c>
       <c r="B64">
-        <v>0.0012111039199793395</v>
+        <v>0.00094139934318067625</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.01151160482552859</v>
       </c>
       <c r="B65">
-        <v>0.0011796174774495369</v>
+        <v>0.00090850029130563187</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.010834451600497496</v>
       </c>
       <c r="B66">
-        <v>0.0011433249523287955</v>
+        <v>0.0008724636623163582</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.010157298375466401</v>
       </c>
       <c r="B67">
-        <v>0.0011018750026415914</v>
+        <v>0.00083284370217697259</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0094801451504353089</v>
       </c>
       <c r="B68">
-        <v>0.0010490444115105377</v>
+        <v>0.00078165014601025949</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.0088029919254042147</v>
       </c>
       <c r="B69">
-        <v>0.000979998180717383</v>
+        <v>0.00071267943512359191</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.0081258387003731222</v>
       </c>
       <c r="B70">
-        <v>0.00090132606158228445</v>
+        <v>0.00063441934640402883</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.0074486854753420288</v>
       </c>
       <c r="B71">
-        <v>0.0008202123602065115</v>
+        <v>0.00055612356592946676</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.0067715322503109346</v>
       </c>
       <c r="B72">
-        <v>0.00073479485227737832</v>
+        <v>0.00047541808096146845</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0060943790252798412</v>
       </c>
       <c r="B73">
-        <v>0.00064200315124125556</v>
+        <v>0.00038837729534604994</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0054172258002487478</v>
       </c>
       <c r="B74">
-        <v>0.00054298075199469393</v>
+        <v>0.00029649697808337605</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0047400725752176544</v>
       </c>
       <c r="B75">
-        <v>0.0004399444353743138</v>
+        <v>0.0002026546721453254</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0040629193501865611</v>
       </c>
       <c r="B76">
-        <v>0.00033519024452683158</v>
+        <v>0.00010983365123648385</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0033857661251554673</v>
       </c>
       <c r="B77">
-        <v>0.00023082903579528749</v>
+        <v>2.0781141304822952E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0027086129001243739</v>
       </c>
       <c r="B78">
-        <v>0.00012815165599791965</v>
+        <v>-6.2805553460848528E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0020314596750932805</v>
       </c>
       <c r="B79">
-        <v>2.9442088179447465E-05</v>
+        <v>-0.0001379501890482387</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.001354306450062187</v>
       </c>
       <c r="B80">
-        <v>-6.12051558124451E-05</v>
+        <v>-0.00019934441371878808</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.00067715322503109348</v>
       </c>
       <c r="B81">
-        <v>-0.00013352814413430291</v>
+        <v>-0.00023374682143890464</v>
       </c>
     </row>
     <row r="82" spans="1:2">
